--- a/artfynd/A 24649-2026 artfynd.xlsx
+++ b/artfynd/A 24649-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>16437514</v>
       </c>
       <c r="B2" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712737.6224707739</v>
+        <v>712738</v>
       </c>
       <c r="R2" t="n">
-        <v>7241859.442885029</v>
+        <v>7241859</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16437582</v>
+        <v>16437510</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712786.0922902079</v>
+        <v>712844</v>
       </c>
       <c r="R3" t="n">
-        <v>7241894.086812443</v>
+        <v>7241944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,26 +854,11 @@
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Över fler olika träd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -905,12 +870,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -932,19 +897,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16437583</v>
+        <v>16437582</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -972,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712772.6876975966</v>
+        <v>712786</v>
       </c>
       <c r="R4" t="n">
-        <v>7241922.151259667</v>
+        <v>7241894</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,19 +965,14 @@
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Över fler olika träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,6 +1006,228 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresa i naturvårdens utmarker</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16437583</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Söder Ladumyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>712773</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7241922</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresa i naturvårdens utmarker</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16437511</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Söder Ladumyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>712785</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7241970</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>stubbe</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Forskningsresa i naturvårdens utmarker</t>
         </is>

--- a/artfynd/A 24649-2026 artfynd.xlsx
+++ b/artfynd/A 24649-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresa i naturvårdens utmarker</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16437514</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Forskningsresa i naturvårdens utmarker</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16437510</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Forskningsresa i naturvårdens utmarker</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16437582</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Forskningsresa i naturvårdens utmarker</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16437583</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,8 +1257,20 @@
           <t>Forskningsresa i naturvårdens utmarker</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16437511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>